--- a/public/static/用户信息导入模板.xlsx
+++ b/public/static/用户信息导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27330" windowHeight="11565"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="用户信息" sheetId="1" r:id="rId1"/>
@@ -28,22 +28,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>序号</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">账户
-</t>
+      <t>账户</t>
     </r>
     <r>
       <rPr>
@@ -62,16 +53,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">姓名
-</t>
+      <t>姓名</t>
     </r>
     <r>
       <rPr>
@@ -87,16 +69,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">手机号
-</t>
+      <t>手机号</t>
     </r>
     <r>
       <rPr>
@@ -115,16 +88,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">部门
-</t>
+      <t>部门</t>
     </r>
     <r>
       <rPr>
@@ -149,6 +113,9 @@
   </si>
   <si>
     <t>用户导入系统后，用户状态默认为启用状态，密码默认为123456</t>
+  </si>
+  <si>
+    <t>部门：输入部门时请输入完整部门，如：宁波市镇海甬明轴承有限公司/仓库部</t>
   </si>
 </sst>
 </file>
@@ -1178,9 +1145,9 @@
     <col min="2" max="2" width="16.5416666666667" style="4" customWidth="1"/>
     <col min="3" max="3" width="12.275" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.3666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="9.275" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.1833333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="24.6333333333333" style="3" customWidth="1"/>
+    <col min="7" max="7" width="36.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="40" customHeight="1" spans="1:7">
@@ -1851,7 +1818,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="6" ht="22" customHeight="1"/>
     <row r="7" ht="22" customHeight="1"/>
     <row r="8" ht="22" customHeight="1"/>

--- a/public/static/用户信息导入模板.xlsx
+++ b/public/static/用户信息导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="用户信息" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,16 @@
   </si>
   <si>
     <r>
-      <t>账户</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">账户
+</t>
     </r>
     <r>
       <rPr>
@@ -53,7 +62,16 @@
   </si>
   <si>
     <r>
-      <t>姓名</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">姓名
+</t>
     </r>
     <r>
       <rPr>
@@ -69,7 +87,16 @@
   </si>
   <si>
     <r>
-      <t>手机号</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">手机号
+</t>
     </r>
     <r>
       <rPr>
@@ -88,7 +115,16 @@
   </si>
   <si>
     <r>
-      <t>部门</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">部门
+</t>
     </r>
     <r>
       <rPr>
@@ -1145,9 +1181,9 @@
     <col min="2" max="2" width="16.5416666666667" style="4" customWidth="1"/>
     <col min="3" max="3" width="12.275" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.3666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.275" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.1833333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="36.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.6333333333333" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="40" customHeight="1" spans="1:7">
